--- a/artfynd/A 49975-2021 artfynd.xlsx
+++ b/artfynd/A 49975-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49975-2021 artfynd.xlsx
+++ b/artfynd/A 49975-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9386,113 +9386,6 @@
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>112606913</v>
-      </c>
-      <c r="B77" t="n">
-        <v>86677</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>816</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Smultronkantarell</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Aphroditeola olida</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>N Holmnäs, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>726694</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7283717</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49975-2021 artfynd.xlsx
+++ b/artfynd/A 49975-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103358751</v>
+        <v>103358743</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>726743.6607343318</v>
+        <v>726745</v>
       </c>
       <c r="R2" t="n">
-        <v>7283773.139453202</v>
+        <v>7283783</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103359188</v>
+        <v>103358786</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726741.7472154472</v>
+        <v>726724</v>
       </c>
       <c r="R3" t="n">
-        <v>7283755.135420498</v>
+        <v>7283708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +847,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103359433</v>
+        <v>103359525</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726726.9386658029</v>
+        <v>726657</v>
       </c>
       <c r="R4" t="n">
-        <v>7283753.143684811</v>
+        <v>7283960</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +948,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103358953</v>
+        <v>103359562</v>
       </c>
       <c r="B5" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>726720.5805395076</v>
+        <v>726640</v>
       </c>
       <c r="R5" t="n">
-        <v>7283685.795592813</v>
+        <v>7283946</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103359453</v>
+        <v>103359692</v>
       </c>
       <c r="B6" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>726719.8677307032</v>
+        <v>726603</v>
       </c>
       <c r="R6" t="n">
-        <v>7283763.799831219</v>
+        <v>7283929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,19 +1150,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103359659</v>
+        <v>103359097</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>816</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>726657.6901806956</v>
+        <v>726701</v>
       </c>
       <c r="R7" t="n">
-        <v>7283931.23061161</v>
+        <v>7283714</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,19 +1251,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,53 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103359525</v>
+        <v>112606913</v>
       </c>
       <c r="B8" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>816</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Laukervägen-östra Kikkejaure, Pi lm</t>
+          <t>N Holmnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726657.0780161627</v>
+        <v>726694</v>
       </c>
       <c r="R8" t="n">
-        <v>7283960.245267826</v>
+        <v>7283716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,22 +1346,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,34 +1365,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103358809</v>
+        <v>103359659</v>
       </c>
       <c r="B9" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,21 +1394,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1530,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726722.0939544081</v>
+        <v>726658</v>
       </c>
       <c r="R9" t="n">
-        <v>7283671.796787212</v>
+        <v>7283931</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,19 +1454,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,37 +1484,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103358759</v>
+        <v>103359707</v>
       </c>
       <c r="B10" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1646,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726775.8117740678</v>
+        <v>726602</v>
       </c>
       <c r="R10" t="n">
-        <v>7283760.713592011</v>
+        <v>7283809</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,19 +1555,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1585,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103359132</v>
+        <v>103359814</v>
       </c>
       <c r="B11" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>1505</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1762,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726749.2046237938</v>
+        <v>726754</v>
       </c>
       <c r="R11" t="n">
-        <v>7283718.351152611</v>
+        <v>7283795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,22 +1653,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,37 +1686,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103359192</v>
+        <v>103358751</v>
       </c>
       <c r="B12" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1878,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726741.7472154472</v>
+        <v>726744</v>
       </c>
       <c r="R12" t="n">
-        <v>7283755.135420498</v>
+        <v>7283773</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,19 +1757,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,37 +1787,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103359814</v>
+        <v>103358764</v>
       </c>
       <c r="B13" t="n">
-        <v>89745</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1505</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726754.4044016722</v>
+        <v>726776</v>
       </c>
       <c r="R13" t="n">
-        <v>7283795.157554523</v>
+        <v>7283761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,22 +1855,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,37 +1888,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103358743</v>
+        <v>103358798</v>
       </c>
       <c r="B14" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2110,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726745.3628555728</v>
+        <v>726734</v>
       </c>
       <c r="R14" t="n">
-        <v>7283783.23790121</v>
+        <v>7283696</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,19 +1959,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,37 +1989,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103359512</v>
+        <v>103358809</v>
       </c>
       <c r="B15" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2226,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>726690.9870745258</v>
+        <v>726722</v>
       </c>
       <c r="R15" t="n">
-        <v>7283824.646105822</v>
+        <v>7283672</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2259,19 +2060,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,15 +2090,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103359491</v>
+        <v>103359222</v>
       </c>
       <c r="B16" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,21 +2101,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3100</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2342,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>726699.3023752865</v>
+        <v>726770</v>
       </c>
       <c r="R16" t="n">
-        <v>7283787.514784181</v>
+        <v>7283766</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,19 +2161,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,37 +2191,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103359016</v>
+        <v>103358953</v>
       </c>
       <c r="B17" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2458,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>726714.1040313827</v>
+        <v>726721</v>
       </c>
       <c r="R17" t="n">
-        <v>7283725.978916012</v>
+        <v>7283686</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2491,19 +2262,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,37 +2292,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103359203</v>
+        <v>103359820</v>
       </c>
       <c r="B18" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,10 +2330,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>726766.5302141024</v>
+        <v>726733</v>
       </c>
       <c r="R18" t="n">
-        <v>7283783.652448222</v>
+        <v>7283754</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2604,22 +2360,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2647,42 +2393,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103359222</v>
+        <v>103359637</v>
       </c>
       <c r="B19" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>2387</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2690,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>726769.6069549718</v>
+        <v>726676</v>
       </c>
       <c r="R19" t="n">
-        <v>7283765.62463509</v>
+        <v>7283896</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2723,19 +2465,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,37 +2495,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103359069</v>
+        <v>103359321</v>
       </c>
       <c r="B20" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2806,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>726704.4946514606</v>
+        <v>726672</v>
       </c>
       <c r="R20" t="n">
-        <v>7283710.692929176</v>
+        <v>7283939</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2839,19 +2566,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2879,37 +2596,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103358980</v>
+        <v>103359325</v>
       </c>
       <c r="B21" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2922,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>726697.2121983018</v>
+        <v>726783</v>
       </c>
       <c r="R21" t="n">
-        <v>7283713.443637212</v>
+        <v>7283732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2955,19 +2667,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,15 +2697,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103359185</v>
+        <v>103359491</v>
       </c>
       <c r="B22" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,21 +2708,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3038,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>726741.7472154472</v>
+        <v>726699</v>
       </c>
       <c r="R22" t="n">
-        <v>7283755.135420498</v>
+        <v>7283788</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,19 +2768,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3111,37 +2798,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103358972</v>
+        <v>103359006</v>
       </c>
       <c r="B23" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>232140</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3154,10 +2836,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>726697.2121983018</v>
+        <v>726711</v>
       </c>
       <c r="R23" t="n">
-        <v>7283713.443637212</v>
+        <v>7283750</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3187,19 +2869,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3227,43 +2899,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103359586</v>
+        <v>103359185</v>
       </c>
       <c r="B24" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3271,10 +2937,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>726640.3168218306</v>
+        <v>726742</v>
       </c>
       <c r="R24" t="n">
-        <v>7283946.06064481</v>
+        <v>7283755</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3304,19 +2970,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3344,37 +3000,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103359308</v>
+        <v>103358993</v>
       </c>
       <c r="B25" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3387,10 +3038,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>726683.0404171816</v>
+        <v>726698</v>
       </c>
       <c r="R25" t="n">
-        <v>7283825.268620066</v>
+        <v>7283725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3420,19 +3071,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3460,15 +3101,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103359385</v>
+        <v>103359132</v>
       </c>
       <c r="B26" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,21 +3112,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3503,10 +3139,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>726752.3291500022</v>
+        <v>726749</v>
       </c>
       <c r="R26" t="n">
-        <v>7283779.216984779</v>
+        <v>7283718</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3536,19 +3172,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3576,15 +3202,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103359562</v>
+        <v>103359203</v>
       </c>
       <c r="B27" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3592,21 +3213,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3240,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>726640.3168218306</v>
+        <v>726767</v>
       </c>
       <c r="R27" t="n">
-        <v>7283946.06064481</v>
+        <v>7283784</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,19 +3273,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3692,15 +3303,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103359006</v>
+        <v>103359220</v>
       </c>
       <c r="B28" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,21 +3314,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3735,10 +3341,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>726710.9877397844</v>
+        <v>726770</v>
       </c>
       <c r="R28" t="n">
-        <v>7283749.816818801</v>
+        <v>7283766</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3768,19 +3374,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3808,37 +3404,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103359065</v>
+        <v>103359245</v>
       </c>
       <c r="B29" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>232140</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3851,10 +3442,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>726704.4946514606</v>
+        <v>726694</v>
       </c>
       <c r="R29" t="n">
-        <v>7283710.692929176</v>
+        <v>7283824</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3884,19 +3475,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3924,15 +3505,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103359074</v>
+        <v>103359279</v>
       </c>
       <c r="B30" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3940,21 +3516,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3967,10 +3543,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>726704.4946514606</v>
+        <v>726710</v>
       </c>
       <c r="R30" t="n">
-        <v>7283710.692929176</v>
+        <v>7283833</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4000,19 +3576,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4040,15 +3606,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103359370</v>
+        <v>103359282</v>
       </c>
       <c r="B31" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4056,21 +3617,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4083,10 +3644,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>726736.4918945935</v>
+        <v>726706</v>
       </c>
       <c r="R31" t="n">
-        <v>7283694.932480662</v>
+        <v>7283837</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4116,19 +3677,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4156,15 +3707,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103359576</v>
+        <v>103359305</v>
       </c>
       <c r="B32" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,27 +3718,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4200,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>726640.3168218306</v>
+        <v>726683</v>
       </c>
       <c r="R32" t="n">
-        <v>7283946.06064481</v>
+        <v>7283825</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4233,27 +3778,18 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4272,15 +3808,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>103359691</v>
+        <v>103359510</v>
       </c>
       <c r="B33" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4288,31 +3819,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4320,10 +3846,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>726602.6156747567</v>
+        <v>726691</v>
       </c>
       <c r="R33" t="n">
-        <v>7283928.573953763</v>
+        <v>7283825</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4353,27 +3879,18 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4392,15 +3909,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>103359510</v>
+        <v>103359857</v>
       </c>
       <c r="B34" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4435,10 +3947,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>726690.9870745258</v>
+        <v>726733</v>
       </c>
       <c r="R34" t="n">
-        <v>7283824.646105822</v>
+        <v>7283754</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4465,22 +3977,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4508,19 +4010,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>103359493</v>
+        <v>103358749</v>
       </c>
       <c r="B35" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4551,10 +4048,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>726699.3023752865</v>
+        <v>726745</v>
       </c>
       <c r="R35" t="n">
-        <v>7283787.514784181</v>
+        <v>7283783</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4584,19 +4081,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4624,15 +4111,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103359282</v>
+        <v>103358753</v>
       </c>
       <c r="B36" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4640,21 +4122,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4667,10 +4149,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>726705.8449261409</v>
+        <v>726744</v>
       </c>
       <c r="R36" t="n">
-        <v>7283836.606289065</v>
+        <v>7283773</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4700,19 +4182,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4740,43 +4212,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>103359637</v>
+        <v>103358774</v>
       </c>
       <c r="B37" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2387</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4784,10 +4250,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>726676.2359661423</v>
+        <v>726732</v>
       </c>
       <c r="R37" t="n">
-        <v>7283896.148351223</v>
+        <v>7283724</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4817,19 +4283,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4857,19 +4313,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>103358749</v>
+        <v>103358980</v>
       </c>
       <c r="B38" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4900,10 +4351,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>726745.3628555728</v>
+        <v>726697</v>
       </c>
       <c r="R38" t="n">
-        <v>7283783.23790121</v>
+        <v>7283713</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4933,19 +4384,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4973,15 +4414,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>103359404</v>
+        <v>103359010</v>
       </c>
       <c r="B39" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4989,21 +4425,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5016,10 +4452,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>726733.3892940911</v>
+        <v>726711</v>
       </c>
       <c r="R39" t="n">
-        <v>7283776.901199509</v>
+        <v>7283750</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5049,19 +4485,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5089,15 +4515,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>103358798</v>
+        <v>103359192</v>
       </c>
       <c r="B40" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5105,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5132,10 +4553,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>726733.5027226716</v>
+        <v>726742</v>
       </c>
       <c r="R40" t="n">
-        <v>7283695.943722802</v>
+        <v>7283755</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5165,19 +4586,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5205,15 +4616,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>103359279</v>
+        <v>103359284</v>
       </c>
       <c r="B41" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5221,21 +4627,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5248,10 +4654,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>726709.8867302067</v>
+        <v>726706</v>
       </c>
       <c r="R41" t="n">
-        <v>7283832.771252596</v>
+        <v>7283837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5281,19 +4687,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5321,15 +4717,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>103359819</v>
+        <v>103359308</v>
       </c>
       <c r="B42" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5337,31 +4728,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5369,10 +4755,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>726732.6903561709</v>
+        <v>726683</v>
       </c>
       <c r="R42" t="n">
-        <v>7283754.009944511</v>
+        <v>7283825</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5399,22 +4785,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5423,6 +4799,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5441,15 +4818,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>103359820</v>
+        <v>103359341</v>
       </c>
       <c r="B43" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5457,21 +4829,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5484,10 +4856,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>726732.6903561709</v>
+        <v>726753</v>
       </c>
       <c r="R43" t="n">
-        <v>7283754.009944511</v>
+        <v>7283707</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5514,22 +4886,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5557,19 +4919,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>103359284</v>
+        <v>103359433</v>
       </c>
       <c r="B44" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5600,10 +4957,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>726705.8449261409</v>
+        <v>726727</v>
       </c>
       <c r="R44" t="n">
-        <v>7283836.606289065</v>
+        <v>7283753</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5633,19 +4990,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5673,37 +5020,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>103358786</v>
+        <v>103359493</v>
       </c>
       <c r="B45" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5716,10 +5058,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>726724.2364323888</v>
+        <v>726699</v>
       </c>
       <c r="R45" t="n">
-        <v>7283708.088799161</v>
+        <v>7283788</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5749,19 +5091,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5789,15 +5121,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>103358993</v>
+        <v>103359512</v>
       </c>
       <c r="B46" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5805,21 +5132,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5832,10 +5159,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>726698.4043097203</v>
+        <v>726691</v>
       </c>
       <c r="R46" t="n">
-        <v>7283724.747879351</v>
+        <v>7283825</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5865,19 +5192,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5905,37 +5222,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>103359707</v>
+        <v>103358759</v>
       </c>
       <c r="B47" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>4365</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5948,10 +5260,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>726602.0479640353</v>
+        <v>726776</v>
       </c>
       <c r="R47" t="n">
-        <v>7283808.539468008</v>
+        <v>7283761</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5981,19 +5293,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6021,37 +5323,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>103359692</v>
+        <v>103359069</v>
       </c>
       <c r="B48" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>4365</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6064,10 +5361,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>726602.6156747567</v>
+        <v>726704</v>
       </c>
       <c r="R48" t="n">
-        <v>7283928.573953763</v>
+        <v>7283711</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6097,19 +5394,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6137,15 +5424,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103359483</v>
+        <v>103359453</v>
       </c>
       <c r="B49" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6153,21 +5435,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6180,10 +5462,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>726709.3622604753</v>
+        <v>726720</v>
       </c>
       <c r="R49" t="n">
-        <v>7283775.847453752</v>
+        <v>7283764</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6213,19 +5495,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6253,15 +5525,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>103359220</v>
+        <v>103359269</v>
       </c>
       <c r="B50" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6269,21 +5536,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6296,10 +5563,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>726769.6069549718</v>
+        <v>726712</v>
       </c>
       <c r="R50" t="n">
-        <v>7283765.62463509</v>
+        <v>7283825</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6329,19 +5596,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6369,15 +5626,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103359289</v>
+        <v>103359320</v>
       </c>
       <c r="B51" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6385,21 +5637,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6437</v>
+        <v>5448</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6412,10 +5664,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>726694.6030487405</v>
+        <v>726685</v>
       </c>
       <c r="R51" t="n">
-        <v>7283852.747815969</v>
+        <v>7283853</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6445,19 +5697,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6485,15 +5727,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>103359320</v>
+        <v>103359404</v>
       </c>
       <c r="B52" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6510,12 +5747,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6528,10 +5765,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>726685.4170691314</v>
+        <v>726733</v>
       </c>
       <c r="R52" t="n">
-        <v>7283853.273127867</v>
+        <v>7283777</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6561,19 +5798,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6601,15 +5828,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>103359321</v>
+        <v>103359429</v>
       </c>
       <c r="B53" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6617,21 +5839,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3100</v>
+        <v>5448</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6644,10 +5866,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>726671.5993955572</v>
+        <v>726727</v>
       </c>
       <c r="R53" t="n">
-        <v>7283939.379248065</v>
+        <v>7283753</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6677,19 +5899,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6717,15 +5929,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>103359325</v>
+        <v>103359462</v>
       </c>
       <c r="B54" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6733,21 +5940,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3100</v>
+        <v>5448</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6760,10 +5967,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>726783.0677440609</v>
+        <v>726710</v>
       </c>
       <c r="R54" t="n">
-        <v>7283731.80268553</v>
+        <v>7283760</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6793,19 +6000,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6833,15 +6030,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>103359122</v>
+        <v>103359137</v>
       </c>
       <c r="B55" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6849,21 +6041,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>5454</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6876,10 +6068,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>726741.1206233241</v>
+        <v>726752</v>
       </c>
       <c r="R55" t="n">
-        <v>7283726.021456472</v>
+        <v>7283714</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6909,19 +6101,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6949,15 +6131,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103358821</v>
+        <v>103359289</v>
       </c>
       <c r="B56" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6965,21 +6142,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5449</v>
+        <v>6437</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6992,10 +6169,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>726724.8490825188</v>
+        <v>726695</v>
       </c>
       <c r="R56" t="n">
-        <v>7283679.071581501</v>
+        <v>7283853</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7025,19 +6202,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7065,42 +6232,38 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>103359110</v>
+        <v>103358776</v>
       </c>
       <c r="B57" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7108,10 +6271,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>726732.4671310883</v>
+        <v>726732</v>
       </c>
       <c r="R57" t="n">
-        <v>7283709.149453824</v>
+        <v>7283724</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7141,28 +6304,17 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7181,42 +6333,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>103359857</v>
+        <v>103359576</v>
       </c>
       <c r="B58" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7224,10 +6372,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>726732.6903561709</v>
+        <v>726640</v>
       </c>
       <c r="R58" t="n">
-        <v>7283754.009944511</v>
+        <v>7283946</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7254,22 +6402,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-08-19</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7278,7 +6416,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7297,43 +6434,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>103359544</v>
+        <v>103359691</v>
       </c>
       <c r="B59" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7341,10 +6477,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>726637.3131000579</v>
+        <v>726603</v>
       </c>
       <c r="R59" t="n">
-        <v>7283957.86536898</v>
+        <v>7283929</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7374,28 +6510,17 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7414,42 +6539,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>103359010</v>
+        <v>103359819</v>
       </c>
       <c r="B60" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7457,10 +6582,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>726710.9877397844</v>
+        <v>726733</v>
       </c>
       <c r="R60" t="n">
-        <v>7283749.816818801</v>
+        <v>7283754</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7487,22 +6612,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7511,7 +6626,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7533,12 +6647,7 @@
         <v>103359334</v>
       </c>
       <c r="B61" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7574,10 +6683,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>726783.0677440609</v>
+        <v>726783</v>
       </c>
       <c r="R61" t="n">
-        <v>7283731.80268553</v>
+        <v>7283732</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7607,19 +6716,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7647,42 +6746,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>103359097</v>
+        <v>103359544</v>
       </c>
       <c r="B62" t="n">
-        <v>86298</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>816</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7690,10 +6785,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>726700.5174162105</v>
+        <v>726637</v>
       </c>
       <c r="R62" t="n">
-        <v>7283713.702794158</v>
+        <v>7283958</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7723,19 +6818,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7763,42 +6848,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>103359508</v>
+        <v>103359586</v>
       </c>
       <c r="B63" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5449</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7806,10 +6887,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>726690.9870745258</v>
+        <v>726640</v>
       </c>
       <c r="R63" t="n">
-        <v>7283824.646105822</v>
+        <v>7283946</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7839,19 +6920,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7879,37 +6950,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>103359429</v>
+        <v>103358972</v>
       </c>
       <c r="B64" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93228</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5448</v>
+        <v>232140</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7922,10 +6988,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>726726.9386658029</v>
+        <v>726697</v>
       </c>
       <c r="R64" t="n">
-        <v>7283753.143684811</v>
+        <v>7283713</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7955,19 +7021,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7995,37 +7051,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>103358764</v>
+        <v>103359065</v>
       </c>
       <c r="B65" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93228</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1962</v>
+        <v>232140</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8038,10 +7089,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>726775.8117740678</v>
+        <v>726704</v>
       </c>
       <c r="R65" t="n">
-        <v>7283760.713592011</v>
+        <v>7283711</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8071,19 +7122,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8108,1283 +7149,6 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>103359305</v>
-      </c>
-      <c r="B66" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Laukervägen-östra Kikkejaure, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>726683.0404171816</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7283825.268620066</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>103359341</v>
-      </c>
-      <c r="B67" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Laukervägen-östra Kikkejaure, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>726752.5573885785</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7283707.403268022</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>103359261</v>
-      </c>
-      <c r="B68" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Laukervägen-östra Kikkejaure, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>726711.7733249452</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7283824.615220926</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>103359462</v>
-      </c>
-      <c r="B69" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Phellodon connatus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Laukervägen-östra Kikkejaure, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>726709.7979742396</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7283759.688540973</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>103359269</v>
-      </c>
-      <c r="B70" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>4745</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tallriska</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Lactarius musteus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Laukervägen-östra Kikkejaure, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>726711.7733249452</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7283824.615220926</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>103359145</v>
-      </c>
-      <c r="B71" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Laukervägen-östra Kikkejaure, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>726749.9929679418</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7283745.401837979</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>103359245</v>
-      </c>
-      <c r="B72" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Laukervägen-östra Kikkejaure, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>726693.9113857665</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7283824.46020189</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr"/>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>103358774</v>
-      </c>
-      <c r="B73" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Laukervägen-östra Kikkejaure, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>726732.1283966787</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7283724.070627844</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="inlineStr"/>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>103359137</v>
-      </c>
-      <c r="B74" t="n">
-        <v>89997</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>5454</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Hornvaxskinn</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Crustoderma corneum</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Laukervägen-östra Kikkejaure, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>726752.4203356149</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7283714.451195358</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>103358753</v>
-      </c>
-      <c r="B75" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Laukervägen-östra Kikkejaure, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>726743.6607343318</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7283773.139453202</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>104160380</v>
-      </c>
-      <c r="B76" t="n">
-        <v>86298</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>816</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Smultronkantarell</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Aphroditeola olida</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>N Holmnäs, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>726694.4744304342</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7283716.550689967</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
